--- a/Incubyte-qa-assignment.xlsx
+++ b/Incubyte-qa-assignment.xlsx
@@ -87,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,6 +102,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -477,7 +480,7 @@
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -528,67 +531,72 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Browser</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Executed By</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Execution Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Defect ID</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
@@ -627,69 +635,75 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Launch Gmail application
-2. Login with valid credentials
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
 3. Navigate to Inbox page
 4. Click on the Compose button
-5. Observe the compose email popup/window</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+5. Verify the compose email window opens successfully</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Compose window opens successfully</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -728,69 +742,75 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Open Gmail and login
-2. Click on Compose button
-3. Enter a valid email address in the To field
-4. Enter subject and body content
-5. Verify that no validation error is displayed</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter a valid recipient email address in the To field
+5. Verify the email address is accepted without validation error</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Valid recipient accepted successfully</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -829,69 +849,75 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. Login to Gmail
-2. Click on Compose button
-3. Place cursor in Subject field
-4. Enter valid subject text
-5. Verify entered subject text is displayed correctly</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter "Incubyte" in the Subject field
+5. Verify the subject text is displayed correctly</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Subject field accepts text successfully</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -930,69 +956,75 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. Login to Gmail
-2. Open Compose email window
-3. Click inside email body section
-4. Enter email message content
-5. Verify text is entered successfully</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter "QA test for Incubyte" in the email body section
+5. Verify the body content is displayed correctly</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Body field accepts text successfully</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1031,70 +1063,78 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. Login to Gmail account
-2. Click on Compose button
-3. Enter valid recipient email address
-4. Enter subject and email body
-5. Click on Send button
-6. Verify confirmation message is displayed</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter valid recipient email address
+5. Enter "Incubyte" in Subject field
+6. Enter "QA test for Incubyte" in email body
+7. Click on Send button
+8. Verify the email is sent successfully</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Email sends successfully successfully</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1133,69 +1173,76 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. Send an email successfully
-2. Navigate to Sent folder
-3. Search for recently sent email
-4. Open the email from Sent folder
-5. Verify email details are correct</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+          <t xml:space="preserve">1. Send an email successfully
+2. Navigate to the Sent folder
+3. Open the recently sent email
+4. Verify recipient email address is correct
+5. Verify subject is "Incubyte"
+6. Verify body contains "QA test for Incubyte" </t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Sent mail visible in Sent folder successfully</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1234,69 +1281,78 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Open Compose email window
-2. Enter recipient, subject and body
-3. Close the compose window without sending
-4. Navigate to Drafts folder
-5. Verify email draft is saved automatically</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter recipient email address
+5. Enter subject and body content
+6. Close the compose window without sending
+7. Open Drafts folder
+8. Verify the draft email is auto-saved</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Draft auto-save works successfully</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1335,69 +1391,75 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+          <t>1. Open Drafts folder in Gmail
+2. Select previously saved draft email
+3. Open the draft email
+4. Verify recipient email address is retained
+5. Verify subject and body content are retained</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Draft reopen works successfully</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1436,69 +1498,77 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Click on attachment icon
+5. Select a valid file from system
+6. Wait for upload completion
+7. Verify attachment is added successfully</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Attachment upload works successfully</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1537,69 +1607,76 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter multiple valid email addresses in To field
+5. Enter subject and body content
+6. Verify all recipients are accepted successfully</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Multiple recipients supported successfully</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1638,69 +1715,76 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Click on CC option
+5. Enter valid email address in CC field
+6. Verify CC recipient is accepted successfully</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>CC functionality works successfully</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1739,69 +1823,76 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Click on BCC option
+5. Enter valid email address in BCC field
+6. Verify BCC recipient is accepted successfully</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>BCC functionality works successfully</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1840,69 +1931,76 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter text in email body
+5. Apply formatting options such as bold or italic
+6. Verify formatting is applied correctly</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Formatting options work successfully</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1941,69 +2039,76 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter text in email body
+5. Insert hyperlink using link option
+6. Verify hyperlink is added successfully</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Hyperlink insertion works successfully</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2042,69 +2147,76 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Click on emoji icon
+5. Select any emoji
+6. Verify emoji appears in email body</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Emoji insertion works successfully</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2143,69 +2255,75 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on the Compose button
+4. Enter misspelled text in email body
+5. Verify spelling suggestions or highlights are displayed</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Spell check works successfully</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2244,69 +2362,75 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Compose an email with valid details
+4. Use keyboard shortcut to send email
+5. Verify email is sent successfully</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Keyboard shortcut send works successfully</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2345,69 +2469,76 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Click on Compose button
+4. Enter email details
+5. Click on minimize icon
+6. Verify compose window is minimized successfully</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Minimize compose window works successfully</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2446,69 +2577,75 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+          <t>1. Open Gmail application
+2. Login with valid Gmail credentials
+3. Open minimized compose window
+4. Click on maximize option
+5. Verify compose window expands successfully</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Maximize compose window works successfully</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2547,69 +2684,76 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. Launch the application
-2. Login with valid credentials
-3. Navigate to the required module/page
-4. Perform the mentioned action
-5. Verify the expected result is displayed</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+          <t xml:space="preserve">1. Send email using valid recipient address
+2. Login to recipient mailbox
+3. Open Inbox folder
+4. Search for recently sent email
+5. Verify subject is "Incubyte"
+6. Verify body contains "QA test for Incubyte" </t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Valid data</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Email received by recipient successfully</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2626,7 +2770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2636,7 +2780,7 @@
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -2687,67 +2831,72 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Browser</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Executed By</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Execution Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Defect ID</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
@@ -2789,69 +2938,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
 3. Leave the To field blank
-4. Enter a valid subject
-5. Enter valid email body content
+4. Enter a "Incubyte"
+5. Enter "QA test for Incubyte"
 6. Click on the Send button
 7. Verify that recipient required validation message is displayed
 8. Verify that the email is not sent and remains in compose/draft state</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Recipient required validation should be displayed and email should not be sent.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2893,69 +3048,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
 3. Enter an invalid email address in the To field, such as user@@test or abc.com
-4. Enter a valid subject
-5. Enter valid email body content
+4. Enter a "Incubyte"
+5. Enter "QA test for Incubyte"
 6. Click on the Send button
 7. Verify that invalid recipient validation is displayed
 8. Verify that the email is not sent until the email address is corrected</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Invalid email validation should be displayed and email should not be sent until corrected.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2998,68 +3159,74 @@
 2. Click on the Compose button
 3. Enter a valid recipient email address
 4. Leave the Subject field blank
-5. Enter valid email body content
+5. Enter "QA test for Incubyte"
 6. Click on the Send button
 7. Verify that a blank subject warning or confirmation message is displayed
 8. Verify that the user can choose to continue sending or cancel and return to compose</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Blank subject warning/confirmation should be displayed before sending.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3108,62 +3275,68 @@
 8. Restore internet and verify the email can be retried or sent based on application behaviour</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Network error, queued status or retry option should be displayed and email content should not be lost.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3204,7 +3377,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter valid recipient, subject and body
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 4. Click on the attachment icon
 5. Select a file larger than the allowed attachment size limit
 6. Wait for upload validation to complete
@@ -3212,62 +3385,68 @@
 8. Verify that a clear size limit message is displayed</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Oversized file should be restricted or handled as per Gmail limit with clear message.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3308,7 +3487,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter valid recipient, subject and body
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 4. Click on the attachment icon
 5. Select an unsupported or restricted file type
 6. Wait for file validation to complete
@@ -3316,62 +3495,68 @@
 8. Verify that a proper unsupported/restricted file message is displayed</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Unsupported/restricted file should be blocked with proper validation message.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3414,68 +3599,74 @@
 2. Click on the Compose button
 3. Enter a valid recipient email address in the To field
 4. Enter the same recipient email address again
-5. Enter valid subject and body
+5. Enter "Incubyte" and body
 6. Click on the Send button
 7. Verify that Gmail handles the duplicate recipient correctly
 8. Verify that the recipient does not receive duplicate copies because of duplicate entry</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Duplicate recipient should be handled properly and duplicate email delivery should be prevented.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3516,7 +3707,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter recipient, subject and body content
+3. Enter recipient, subject as "Incubyte" and body as "QA test for Incubyte" content
 4. Keep the session idle until timeout or simulate session expiry
 5. Try to send or save the email
 6. Verify that the user is asked to login again
@@ -3524,62 +3715,68 @@
 8. Verify that the email is not sent without valid session authentication</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>User should be asked to re-authenticate and email should not be sent without valid session.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3620,70 +3817,76 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter recipient, subject and body content
+3. Enter recipient, subject as "Incubyte" and body as "QA test for Incubyte" content
 4. Refresh the browser page before sending the email
 5. After page reload, navigate to Drafts folder
 6. Open the latest draft email
-7. Verify that recipient, subject and body are retained
+7. Verify that recipient, subject as "Incubyte" and body as "QA test for Incubyte" are retained
 8. Verify that no duplicate or corrupted draft is created</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Draft content should be retained after browser refresh.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3724,7 +3927,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter valid recipient, subject and body
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 4. Start uploading a valid attachment
 5. Disconnect the internet while the attachment is uploading
 6. Verify that upload failure, retry, or paused upload status is shown
@@ -3732,62 +3935,68 @@
 8. Verify that the attachment can be uploaded again and incomplete attachment is not sent</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Upload failure/retry status should be shown and incomplete attachment should not be sent.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3830,68 +4039,74 @@
 2. Click on the Compose button
 3. Click on the CC option
 4. Enter an invalid email address in the CC field
-5. Enter valid To recipient, subject and body
+5. Enter valid To recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 6. Click on the Send button
 7. Verify that validation message is displayed for invalid CC email
 8. Verify that the email is not sent until the CC value is corrected or removed</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Invalid CC validation should be displayed and email should not be sent until corrected.</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3934,68 +4149,74 @@
 2. Click on the Compose button
 3. Click on the BCC option
 4. Enter an invalid email address in the BCC field
-5. Enter valid To recipient, subject and body
+5. Enter valid To recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 6. Click on the Send button
 7. Verify that validation message is displayed for invalid BCC email
 8. Verify that the email is not sent until the BCC value is corrected or removed</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Invalid BCC validation should be displayed and email should not be sent until corrected.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4036,7 +4257,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter valid recipient, subject and body
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 4. Click the Send button multiple times quickly
 5. Observe the send action and confirmation message
 6. Open the Sent folder
@@ -4044,62 +4265,68 @@
 8. Verify that the recipient receives only one email</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Only one email should be sent and duplicate send should be prevented.</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4141,69 +4368,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
 3. Enter a valid recipient email address
-4. Enter special characters in subject and body, such as @ # ₹ % &amp; * ( ) - _ + =
+4. Enter special characters in subject as "Incubyte" and body as "QA test for Incubyte", such as @ # ₹ % &amp; * ( ) - _ + =
 5. Click on the Send button
 6. Open the sent email from Sent folder
 7. Verify that valid special characters are displayed correctly
 8. Verify that formatting and content are not corrupted</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Valid special characters should be accepted and displayed correctly.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4245,69 +4478,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
 3. Enter a valid recipient email address
-4. Enter a valid subject
+4. Enter a "Incubyte"
 5. Leave the email body blank
 6. Click on the Send button
 7. Verify whether Gmail allows sending blank body email or shows confirmation as per expected behaviour
 8. Verify that the email is handled correctly and no application error occurs</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Blank body email should be handled as per Gmail behaviour without application error.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4348,7 +4587,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter valid recipient, subject and body
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 4. Try to attach a corrupted file or file with invalid extension/content mismatch
 5. Wait for upload/validation to complete
 6. Verify that the file is rejected or safely handled
@@ -4356,62 +4595,68 @@
 8. Verify that the email is not sent with a corrupted or incomplete attachment</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Invalid/corrupted attachment should be rejected or safely handled.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4460,62 +4705,68 @@
 8. Verify that the subject is saved/sent according to Gmail allowed limit and behaviour</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Application should remain stable and handle subject according to allowed limit.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4564,62 +4815,68 @@
 8. Verify that the email body is saved/sent without truncation beyond allowed behaviour</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Application should remain responsive and preserve body content as per allowed behaviour.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4661,69 +4918,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
 3. Add recipients more than the allowed limit in the To/CC/BCC fields
-4. Enter valid subject and body
+4. Enter "Incubyte" and body
 5. Click on the Send button
 6. Verify that the system displays recipient limit or validation message
 7. Verify that the email is not sent beyond the allowed recipient limit
 8. Remove extra recipients and verify the email can be sent within allowed limit</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Recipient limit validation should be displayed and excessive recipients should be restricted.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4765,69 +5028,75 @@
           <t>1. Open Gmail using an unsupported or outdated browser version
 2. Login with valid credentials if login is supported
 3. Try to open the Compose email window
-4. Enter recipient, subject and body if compose window opens
+4. Enter recipient, subject as "Incubyte" and body as "QA test for Incubyte" if compose window opens
 5. Try to send the email
 6. Verify that compatibility warning is shown if browser is unsupported
 7. Verify that compose functionality does not break unexpectedly
 8. Verify that the application fails gracefully without crash or data loss</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Invalid data</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Compatibility warning or graceful handling should be shown without crash.</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4844,7 +5113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4905,67 +5174,72 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Browser</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Executed By</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Execution Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Defect ID</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
@@ -5016,66 +5290,72 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>Recipient: valid email
 Payload: harmless script-like test string</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Script-like input should not execute. It should be safely encoded/sanitised and displayed as plain text without breaking the page.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5117,7 +5397,7 @@
           <t>1. Login to Gmail with valid user credentials.
 2. Click on the Compose button.
 3. Enter a valid recipient email address.
-4. Enter SQL-style special character text in Subject and Body, for example: ' OR '1'='1.
+4. Enter SQL-style special character text in subject as "Incubyte" and body as "QA test for Incubyte", for example: ' OR '1'='1.
 5. Click on Send.
 6. Verify the email is handled normally as plain text content.
 7. Confirm there is no application error, data exposure, page crash or abnormal behaviour.
@@ -5126,66 +5406,72 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>Recipient: valid email
 Payload: SQL-style special character text</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>SQL-style input should be treated only as plain text. Application should not show errors, expose data, or behave abnormally.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5226,7 +5512,7 @@
         <is>
           <t>1. Login to Gmail with valid user credentials.
 2. Click on the Compose button.
-3. Enter a valid recipient email address, subject and body.
+3. Enter a valid recipient email address, subject as "Incubyte" and body as "QA test for Incubyte".
 4. Try to attach a test file that represents an unsafe or blocked file type as per security policy.
 5. Wait for the attachment validation/scanning result.
 6. Verify the unsafe attachment is blocked, rejected or flagged.
@@ -5236,66 +5522,72 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>Valid recipient
 Test unsafe/blocked attachment file</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Unsafe attachments should be blocked or flagged before sending, and the user should see a clear warning message.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5335,7 +5627,7 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Open Gmail in a browser and login with valid credentials.
-2. Open Compose and enter valid email details.
+2. Open Compose and Enter subject as "Incubyte" and body as "QA test for Incubyte".
 3. In another tab, logout from Gmail or invalidate the session.
 4. Return to the compose tab.
 5. Click on Send.
@@ -5346,65 +5638,71 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>Valid email content with expired/logged-out session</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Email send should be blocked when the session is invalid or unauthorised. User should be asked to authenticate again.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5455,65 +5753,71 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>Dummy sensitive-looking test data only; do not use real sensitive data</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Sensitive-looking data should not be exposed in logs, error messages or unintended UI areas.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5553,7 +5857,7 @@
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Login to Gmail with valid user credentials.
-2. Open Compose and enter valid email details.
+2. Open Compose and Enter subject as "Incubyte" and body as "QA test for Incubyte".
 3. Simulate an expired or invalid session by logging out from another tab or clearing the active session as permitted in the test environment.
 4. Return to the compose screen.
 5. Attempt to send the email.
@@ -5564,65 +5868,71 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>Valid email details with expired/invalid session</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Invalid or expired sessions should not be allowed to send emails. User should be forced to re-authenticate.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5673,65 +5983,71 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>Safe dummy suspicious-looking URL</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Suspicious links should be safely handled. Warning should appear if this control is configured, and no link should open automatically.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5772,7 +6088,7 @@
         <is>
           <t>1. Login to Gmail with valid user credentials.
 2. Click on Compose.
-3. Enter valid recipient, subject and body.
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte".
 4. Attach a test file that should be scanned as per attachment security rules.
 5. Wait until upload/scanning is completed.
 6. Verify the scan status or validation result is shown correctly.
@@ -5782,65 +6098,71 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>Safe test file and blocked test file as per QA environment policy</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Attachments should be scanned/validated before sending. Unsafe files should be blocked and safe files should be allowed.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5891,65 +6213,71 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>Unauthenticated user session and valid login credentials</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Compose and send functionality should be accessible only after successful authentication.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -5990,7 +6318,7 @@
         <is>
           <t>1. Login using a test account with limited or restricted access, if available.
 2. Try to open the Compose email feature.
-3. Try to send an email using valid recipient, subject and body.
+3. Try to send an email using valid recipient, subject as "Incubyte" and body as "QA test for Incubyte".
 4. Verify whether the user role/permission allows the action.
 5. If access is not allowed, confirm the action is blocked with an appropriate message.
 6. If access is allowed, confirm the email sends only within the permitted access scope.
@@ -6000,65 +6328,71 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>Restricted/limited access test account and valid email details</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Access control should be enforced. Users should only perform actions allowed by their role or permissions.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>Security validation steps updated with clear tester-friendly actions and safe test data.</t>
         </is>
@@ -6075,7 +6409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6085,7 +6419,7 @@
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -6136,67 +6470,72 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Browser</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Executed By</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Execution Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Defect ID</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
@@ -6245,62 +6584,68 @@
 8. Verify that compose window opens within the acceptable response time and page remains responsive</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Compose window should become usable within acceptable response time.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6342,69 +6687,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Start browser developer tools or performance monitoring tool
 3. Click on the Compose button
-4. Enter valid recipient, subject and body
+4. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 5. Click on the Send button and start measuring response time
 6. Stop measuring when send confirmation/queued status is displayed
 7. Repeat the test with normal network condition
 8. Verify that send response time is within acceptable limit</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Send confirmation or queued status should appear within acceptable response time.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6445,7 +6796,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter valid recipient, subject and body
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 4. Attach a large supported file within allowed size limit
 5. Monitor upload progress, browser responsiveness and completion time
 6. Verify that the user can continue using the compose window during upload
@@ -6453,62 +6804,68 @@
 8. Verify that upload and send complete within acceptable performance range</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Large supported attachment should upload within acceptable time and UI should remain responsive.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6549,7 +6906,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Create multiple compose emails one by one
-3. Enter different recipient, subject and body for each draft
+3. Enter different recipient, subject as "Incubyte" and body as "QA test for Incubyte" for each draft
 4. Close each compose window to save as draft
 5. Open the Drafts folder
 6. Measure time taken to load and open drafts
@@ -6557,62 +6914,68 @@
 8. Verify that Drafts folder remains responsive with multiple drafts</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Multiple drafts should save and load without noticeable delay.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6655,68 +7018,74 @@
 2. Click on the Compose button
 3. Add a high number of valid recipients within the allowed limit
 4. Observe typing, auto-suggestion and chip creation behaviour
-5. Enter subject and body
+5. Enter subject as "Incubyte" and body as "QA test for Incubyte"
 6. Click Send and measure response time
 7. Verify that the recipient field remains responsive
 8. Verify that send action completes within acceptable time</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Recipient field and send action should remain responsive within allowed recipient limit.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6758,69 +7127,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Open the first compose window and enter draft content
 3. Open additional compose windows using supported Gmail behaviour
-4. Enter different recipient, subject and body in each compose window
+4. Enter different recipient, subject as "Incubyte" and body as "QA test for Incubyte" in each compose window
 5. Switch between compose windows and update content
 6. Monitor browser responsiveness and memory usage
 7. Send or save each email separately
 8. Verify that each compose window works independently without delay or data mix-up</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Multiple compose windows should work independently without lag or data mix-up.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6869,62 +7244,68 @@
 8. Verify that Gmail does not crash, freeze or become unusable</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Memory usage should remain stable without abnormal increase, crash or freeze.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6966,69 +7347,75 @@
           <t>1. Open Gmail and login with valid credentials
 2. Start browser performance monitoring
 3. Open the Compose window
-4. Type continuously in subject and body fields
+4. Type continuously in subject as "Incubyte" and body as "QA test for Incubyte" fields
 5. Apply formatting, add recipients and attach a small file
 6. Scroll, minimize and maximize the compose window
 7. Observe input delay, UI lag and page responsiveness
 8. Verify that the browser remains responsive during compose operations</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Browser should remain responsive during typing, formatting and attachment actions.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7069,7 +7456,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials
 2. Click on the Compose button
-3. Enter recipient, subject and body content
+3. Enter recipient, subject as "Incubyte" and body as "QA test for Incubyte" content
 4. Modify the content multiple times
 5. Observe auto-save status or wait for draft sync
 6. Close the compose window
@@ -7077,62 +7464,68 @@
 8. Verify that auto-save completes within acceptable time and latest content is retained</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Draft auto-save should complete within acceptable time and latest content should be retained.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7173,7 +7566,7 @@
         <is>
           <t>1. Open Gmail and login with valid credentials using stable internet
 2. Click on the Compose button
-3. Enter valid recipient, subject and body
+3. Enter valid recipient, subject as "Incubyte" and body as "QA test for Incubyte"
 4. Select a supported attachment file of known size
 5. Start measuring upload time when upload begins
 6. Stop measuring when upload completes successfully
@@ -7181,62 +7574,68 @@
 8. Verify that upload speed and completion time are acceptable for the network condition</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Incubyte
+Body: QA test for Incubyte</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Performance data</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Attachment upload should complete within acceptable time based on file size and network condition.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Chrome</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Priyanka Patil</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>23-May-2026</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7253,7 +7652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7307,6 +7706,16 @@
           <t>Expected Result</t>
         </is>
       </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Assignment Email Subject</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Assignment Email Body</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="125" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -7352,6 +7761,16 @@
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Compose window opens successfully</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Incubyte</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>QA test for Incubyte</t>
         </is>
       </c>
     </row>
@@ -10939,7 +11358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11088,6 +11507,37 @@
         <v>60</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Assignment Test Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Email Subject</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Incubyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Email Body</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>QA test for Incubyte</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
